--- a/code/data/combined/pelg+jmul-w0wacdm-free.xlsx
+++ b/code/data/combined/pelg+jmul-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>543831.9299777084</v>
+        <v>543831.9299773461</v>
       </c>
       <c r="C2" t="n">
-        <v>-985857.6471275089</v>
+        <v>-985857.647126727</v>
       </c>
       <c r="D2" t="n">
-        <v>74888.07319705308</v>
+        <v>74888.07319681242</v>
       </c>
       <c r="E2" t="n">
-        <v>221829.0705371632</v>
+        <v>221829.0705370136</v>
       </c>
       <c r="F2" t="n">
-        <v>-10062.16793671883</v>
+        <v>-10062.16793661591</v>
       </c>
       <c r="G2" t="n">
-        <v>-22067.40475040138</v>
+        <v>-22067.40475038347</v>
       </c>
       <c r="H2" t="n">
-        <v>-8468.205857395506</v>
+        <v>-8468.205857388459</v>
       </c>
       <c r="I2" t="n">
-        <v>-19574.61342723671</v>
+        <v>-19574.61342722942</v>
       </c>
       <c r="J2" t="n">
-        <v>-1859.91350585721</v>
+        <v>-1859.913505858945</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-985857.6471274106</v>
+        <v>-985857.6471269778</v>
       </c>
       <c r="C3" t="n">
-        <v>2505464.02506994</v>
+        <v>2505464.025068933</v>
       </c>
       <c r="D3" t="n">
-        <v>-410464.0118392218</v>
+        <v>-410464.0118386716</v>
       </c>
       <c r="E3" t="n">
-        <v>-423082.6601528154</v>
+        <v>-423082.6601526163</v>
       </c>
       <c r="F3" t="n">
-        <v>44839.01953074498</v>
+        <v>44839.0195304135</v>
       </c>
       <c r="G3" t="n">
-        <v>42500.38954622936</v>
+        <v>42500.38954619964</v>
       </c>
       <c r="H3" t="n">
-        <v>21380.7114602964</v>
+        <v>21380.7114602873</v>
       </c>
       <c r="I3" t="n">
-        <v>10982.37632595422</v>
+        <v>10982.37632594415</v>
       </c>
       <c r="J3" t="n">
-        <v>137.4427839585148</v>
+        <v>137.4427839640779</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74888.07319673034</v>
+        <v>74888.07319728662</v>
       </c>
       <c r="C4" t="n">
-        <v>-410464.01183863</v>
+        <v>-410464.0118397843</v>
       </c>
       <c r="D4" t="n">
-        <v>285152.2969911307</v>
+        <v>285152.2969912172</v>
       </c>
       <c r="E4" t="n">
-        <v>48556.94444967611</v>
+        <v>48556.94444989473</v>
       </c>
       <c r="F4" t="n">
-        <v>-98803.12100754482</v>
+        <v>-98803.1210074644</v>
       </c>
       <c r="G4" t="n">
-        <v>-5392.025980868662</v>
+        <v>-5392.025980886649</v>
       </c>
       <c r="H4" t="n">
-        <v>-4066.114502408726</v>
+        <v>-4066.114502419124</v>
       </c>
       <c r="I4" t="n">
-        <v>16151.8096162848</v>
+        <v>16151.80961627983</v>
       </c>
       <c r="J4" t="n">
-        <v>5443.117187486381</v>
+        <v>5443.117187485876</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>221829.0705371413</v>
+        <v>221829.0705370794</v>
       </c>
       <c r="C5" t="n">
-        <v>-423082.660152922</v>
+        <v>-423082.6601527163</v>
       </c>
       <c r="D5" t="n">
-        <v>48556.94444989328</v>
+        <v>48556.94444971585</v>
       </c>
       <c r="E5" t="n">
-        <v>103838.2184716795</v>
+        <v>103838.2184716427</v>
       </c>
       <c r="F5" t="n">
-        <v>-17728.69561114328</v>
+        <v>-17728.69561103278</v>
       </c>
       <c r="G5" t="n">
-        <v>-10113.71201078944</v>
+        <v>-10113.71201078272</v>
       </c>
       <c r="H5" t="n">
-        <v>-3841.449517845791</v>
+        <v>-3841.449517843875</v>
       </c>
       <c r="I5" t="n">
-        <v>-7218.068523301677</v>
+        <v>-7218.06852330227</v>
       </c>
       <c r="J5" t="n">
-        <v>-727.9858571006075</v>
+        <v>-727.9858571028482</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-10062.16793657067</v>
+        <v>-10062.16793663615</v>
       </c>
       <c r="C6" t="n">
-        <v>44839.01953037023</v>
+        <v>44839.01953065772</v>
       </c>
       <c r="D6" t="n">
-        <v>-98803.12100747152</v>
+        <v>-98803.12100764105</v>
       </c>
       <c r="E6" t="n">
-        <v>-17728.69561105482</v>
+        <v>-17728.6956110996</v>
       </c>
       <c r="F6" t="n">
-        <v>82575.2671729359</v>
+        <v>82575.26717299993</v>
       </c>
       <c r="G6" t="n">
-        <v>3933.386347634116</v>
+        <v>3933.386347638802</v>
       </c>
       <c r="H6" t="n">
-        <v>457.3309523560218</v>
+        <v>457.3309523587195</v>
       </c>
       <c r="I6" t="n">
-        <v>-1790.426177908704</v>
+        <v>-1790.426177918705</v>
       </c>
       <c r="J6" t="n">
-        <v>-1869.841147278033</v>
+        <v>-1869.84114728118</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-22067.40475041224</v>
+        <v>-22067.40475037404</v>
       </c>
       <c r="C7" t="n">
-        <v>42500.38954628393</v>
+        <v>42500.38954618186</v>
       </c>
       <c r="D7" t="n">
-        <v>-5392.025980907822</v>
+        <v>-5392.025980868599</v>
       </c>
       <c r="E7" t="n">
-        <v>-10113.71201079712</v>
+        <v>-10113.71201077771</v>
       </c>
       <c r="F7" t="n">
-        <v>3933.386347647882</v>
+        <v>3933.386347630236</v>
       </c>
       <c r="G7" t="n">
-        <v>1160.792167776852</v>
+        <v>1160.792167774609</v>
       </c>
       <c r="H7" t="n">
-        <v>371.7432495565523</v>
+        <v>371.7432495556183</v>
       </c>
       <c r="I7" t="n">
-        <v>923.7065237632842</v>
+        <v>923.7065237634415</v>
       </c>
       <c r="J7" t="n">
-        <v>84.40059098081481</v>
+        <v>84.40059098121415</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-8468.205857401921</v>
+        <v>-8468.205857394418</v>
       </c>
       <c r="C8" t="n">
-        <v>21380.71146033292</v>
+        <v>21380.71146029614</v>
       </c>
       <c r="D8" t="n">
-        <v>-4066.114502432123</v>
+        <v>-4066.114502404919</v>
       </c>
       <c r="E8" t="n">
-        <v>-3841.449517849536</v>
+        <v>-3841.44951784308</v>
       </c>
       <c r="F8" t="n">
-        <v>457.3309523642332</v>
+        <v>457.3309523495588</v>
       </c>
       <c r="G8" t="n">
-        <v>371.7432495564606</v>
+        <v>371.7432495555609</v>
       </c>
       <c r="H8" t="n">
-        <v>198.3591353866939</v>
+        <v>198.3591353863482</v>
       </c>
       <c r="I8" t="n">
-        <v>63.60759361185721</v>
+        <v>63.60759361270657</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.059102422924663</v>
+        <v>-6.059102422526317</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-19574.61342729525</v>
+        <v>-19574.61342718943</v>
       </c>
       <c r="C9" t="n">
-        <v>10982.37632612211</v>
+        <v>10982.37632585235</v>
       </c>
       <c r="D9" t="n">
-        <v>16151.80961622383</v>
+        <v>16151.80961630852</v>
       </c>
       <c r="E9" t="n">
-        <v>-7218.068523337935</v>
+        <v>-7218.068523287437</v>
       </c>
       <c r="F9" t="n">
-        <v>-1790.426177894434</v>
+        <v>-1790.426177923834</v>
       </c>
       <c r="G9" t="n">
-        <v>923.7065237675727</v>
+        <v>923.7065237622385</v>
       </c>
       <c r="H9" t="n">
-        <v>63.60759361444974</v>
+        <v>63.60759361198606</v>
       </c>
       <c r="I9" t="n">
-        <v>3290.39690631434</v>
+        <v>3290.396906315053</v>
       </c>
       <c r="J9" t="n">
-        <v>655.4756848043892</v>
+        <v>655.4756848052625</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1859.913505873971</v>
+        <v>-1859.913505848777</v>
       </c>
       <c r="C10" t="n">
-        <v>137.4427840081107</v>
+        <v>137.442783939914</v>
       </c>
       <c r="D10" t="n">
-        <v>5443.117187469337</v>
+        <v>5443.117187494518</v>
       </c>
       <c r="E10" t="n">
-        <v>-727.9858571106557</v>
+        <v>-727.9858570980239</v>
       </c>
       <c r="F10" t="n">
-        <v>-1869.841147274233</v>
+        <v>-1869.841147284016</v>
       </c>
       <c r="G10" t="n">
-        <v>84.40059098202924</v>
+        <v>84.4005909806543</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.059102422186511</v>
+        <v>-6.059102422811863</v>
       </c>
       <c r="I10" t="n">
-        <v>655.4756848044706</v>
+        <v>655.4756848048723</v>
       </c>
       <c r="J10" t="n">
-        <v>196.195825382449</v>
+        <v>196.1958253827471</v>
       </c>
     </row>
   </sheetData>
